--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486916_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486916_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.284</v>
+        <v>7.9133</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7267</v>
+        <v>6.5635</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5574</v>
+        <v>1.3499</v>
       </c>
       <c r="G2" t="n">
         <v>1.1036</v>
@@ -610,13 +610,13 @@
         <v>3.6962</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5912</v>
+        <v>-0.9619</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.4415</v>
+        <v>-0.6046</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1497</v>
+        <v>-0.3572</v>
       </c>
       <c r="V2" t="n">
         <v>6.1289</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. AGUILAR HERNANDEZ</t>
+          <t>A. GARCIA BORREGO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0682</v>
+        <v>2.6686</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7806</v>
+        <v>0.2174</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7124</v>
+        <v>2.4512</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8319</v>
+        <v>1.1663</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7851</v>
+        <v>-0.6257</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0469</v>
+        <v>1.792</v>
       </c>
       <c r="J3" t="n">
-        <v>4.7493</v>
+        <v>0.0897</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1714</v>
+        <v>-1.2127</v>
       </c>
       <c r="L3" t="n">
-        <v>3.578</v>
+        <v>1.3024</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9174</v>
+        <v>1.0766</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3863</v>
+        <v>0.587</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5311</v>
+        <v>0.4897</v>
       </c>
       <c r="P3" t="n">
-        <v>0.616</v>
+        <v>1.8481</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3185</v>
+        <v>0.0077</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4225</v>
+        <v>0.1277</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7409</v>
+        <v>-0.12</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.6982</v>
+        <v>-0.3536</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4805</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1786</v>
+        <v>-0.3536</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. GARCIA BORREGO</t>
+          <t>V. AGUILAR HERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0211</v>
+        <v>2.5173</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5699</v>
+        <v>3.4668</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4512</v>
+        <v>-0.9495</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1663</v>
+        <v>2.8319</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6257</v>
+        <v>0.7851</v>
       </c>
       <c r="I4" t="n">
-        <v>1.792</v>
+        <v>2.0469</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0897</v>
+        <v>4.7493</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2127</v>
+        <v>1.1714</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3024</v>
+        <v>3.578</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0766</v>
+        <v>-1.9174</v>
       </c>
       <c r="N4" t="n">
-        <v>0.587</v>
+        <v>-0.3863</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4897</v>
+        <v>-1.5311</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8481</v>
+        <v>0.616</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8481</v>
+        <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3603</v>
+        <v>-0.2325</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4802</v>
+        <v>-0.7363</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.12</v>
+        <v>0.5038</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3536</v>
+        <v>-0.6982</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.4805</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3536</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0286</v>
+        <v>1.9816</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2385</v>
+        <v>1.9247</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2099</v>
+        <v>0.0569</v>
       </c>
       <c r="G5" t="n">
         <v>0.4011</v>
@@ -844,13 +844,13 @@
         <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6785</v>
+        <v>-0.7255</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.159</v>
+        <v>-0.4728</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5195</v>
+        <v>-0.2527</v>
       </c>
       <c r="V5" t="n">
         <v>0.4579</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6723</v>
+        <v>1.3732</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5142</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1865</v>
+        <v>1.3644</v>
       </c>
       <c r="G6" t="n">
         <v>0.5897</v>
@@ -922,13 +922,13 @@
         <v>2.0534</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.377</v>
+        <v>-0.6761</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5851</v>
+        <v>-0.0621</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7919</v>
+        <v>-0.614</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5938</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3416</v>
+        <v>-1.4305</v>
       </c>
       <c r="E7" t="n">
         <v>-1.2921</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0494</v>
+        <v>-0.1384</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6197</v>
@@ -1000,13 +1000,13 @@
         <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4118</v>
+        <v>-0.5008</v>
       </c>
       <c r="T7" t="n">
         <v>-0.6587</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2469</v>
+        <v>0.158</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1314</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. HIERREZUELO SERER</t>
+          <t>A. VERA PICAZO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9362</v>
+        <v>-2.6497</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6981</v>
+        <v>-3.3517</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7619</v>
+        <v>0.702</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.4803</v>
+        <v>0.0514</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.0489</v>
+        <v>1.0251</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4314</v>
+        <v>-0.9736</v>
       </c>
       <c r="J8" t="n">
-        <v>-3.8098</v>
+        <v>-0.4573</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.1914</v>
+        <v>0.2404</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6183999999999999</v>
+        <v>-0.6977</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3294</v>
+        <v>0.5087</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1425</v>
+        <v>0.7846</v>
       </c>
       <c r="O8" t="n">
-        <v>0.187</v>
+        <v>-0.2759</v>
       </c>
       <c r="P8" t="n">
-        <v>2.0534</v>
+        <v>1.0267</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0534</v>
+        <v>3.0801</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2587</v>
+        <v>-1.0171</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1117</v>
+        <v>-0.841</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1469</v>
+        <v>-0.1761</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.7679</v>
+        <v>-2.7109</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.7679</v>
+        <v>-2.7109</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7653</v>
+        <v>-2.846</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3371</v>
+        <v>-0.062</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4283</v>
+        <v>-2.784</v>
       </c>
       <c r="G9" t="n">
         <v>-3.6984</v>
@@ -1156,13 +1156,13 @@
         <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3339</v>
+        <v>-0.4145</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9881</v>
+        <v>-0.713</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6542</v>
+        <v>0.2985</v>
       </c>
       <c r="V9" t="n">
         <v>0.2402</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. VERA PICAZO</t>
+          <t>J. HIERREZUELO SERER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8628</v>
+        <v>-2.9073</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1498</v>
+        <v>-3.6395</v>
       </c>
       <c r="F10" t="n">
-        <v>0.287</v>
+        <v>0.7322</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0514</v>
+        <v>-3.4803</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0251</v>
+        <v>-3.0489</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9736</v>
+        <v>-0.4314</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4573</v>
+        <v>-3.8098</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2404</v>
+        <v>-3.1914</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6977</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5087</v>
+        <v>0.3294</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7846</v>
+        <v>0.1425</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2759</v>
+        <v>0.187</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0267</v>
+        <v>2.0534</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.0801</v>
+        <v>2.0534</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.2301</v>
+        <v>0.2876</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.6391</v>
+        <v>0.1703</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5911</v>
+        <v>0.1173</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.7109</v>
+        <v>-1.7679</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7109</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6078</v>
+        <v>-4.9447</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6781</v>
+        <v>-2.9261</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9297</v>
+        <v>-2.0186</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6301</v>
@@ -1312,13 +1312,13 @@
         <v>1.0267</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3305</v>
+        <v>-0.6674</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2249</v>
+        <v>-0.4728</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1056</v>
+        <v>-0.1946</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5938</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.9524</v>
+        <v>-6.5654</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3785</v>
+        <v>-4.1693</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.574</v>
+        <v>-2.3961</v>
       </c>
       <c r="G12" t="n">
         <v>-4.7141</v>
@@ -1390,13 +1390,13 @@
         <v>1.0267</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9508</v>
+        <v>-0.5638</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.1198</v>
+        <v>-0.9106</v>
       </c>
       <c r="U12" t="n">
-        <v>0.169</v>
+        <v>0.3468</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2875</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.5531</v>
+        <v>-7.7261</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.9329</v>
+        <v>-7.0762</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6202</v>
+        <v>-0.6499</v>
       </c>
       <c r="G13" t="n">
         <v>-5.5922</v>
@@ -1468,13 +1468,13 @@
         <v>1.4374</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0779</v>
+        <v>-0.2509</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5542</v>
+        <v>-0.6975</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4763</v>
+        <v>0.4467</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2402</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.945</v>
+        <v>-12.6157</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.6651</v>
+        <v>-10.3357</v>
       </c>
       <c r="F14" t="n">
         <v>-2.2799</v>
@@ -1519,10 +1519,10 @@
         <v>-9.288</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4165000000000005</v>
+        <v>-0.4164999999999996</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.531899999999999</v>
+        <v>-3.5319</v>
       </c>
       <c r="L14" t="n">
         <v>3.1153</v>
@@ -1546,16 +1546,16 @@
         <v>21.5609</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.0442</v>
+        <v>-5.715199999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.200999999999999</v>
+        <v>-5.8714</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1564</v>
+        <v>0.1565</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.5503</v>
+        <v>-1.550300000000001</v>
       </c>
       <c r="W14" t="n">
         <v>8.273099999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.2349</v>
+        <v>7.0483</v>
       </c>
       <c r="E15" t="n">
         <v>2.3851</v>
       </c>
       <c r="F15" t="n">
-        <v>4.8498</v>
+        <v>4.6632</v>
       </c>
       <c r="G15" t="n">
         <v>6.7319</v>
@@ -1624,13 +1624,13 @@
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>0.887</v>
+        <v>0.7004</v>
       </c>
       <c r="T15" t="n">
         <v>-0.2753</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1623</v>
+        <v>0.9757</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5893</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3672</v>
+        <v>2.8136</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1935</v>
+        <v>1.4027</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1737</v>
+        <v>1.4108</v>
       </c>
       <c r="G16" t="n">
         <v>0.6857</v>
@@ -1702,13 +1702,13 @@
         <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0922</v>
+        <v>0.5386</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2171</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3093</v>
+        <v>0.5465</v>
       </c>
       <c r="V16" t="n">
         <v>1.1786</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8451</v>
+        <v>2.4587</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4634</v>
+        <v>0.2688</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3085</v>
+        <v>2.1899</v>
       </c>
       <c r="G17" t="n">
         <v>-1.9381</v>
@@ -1780,13 +1780,13 @@
         <v>1.0267</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3007</v>
+        <v>0.9144</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9145</v>
+        <v>-0.1823</v>
       </c>
       <c r="U17" t="n">
-        <v>1.2152</v>
+        <v>1.0966</v>
       </c>
       <c r="V17" t="n">
         <v>4.7145</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. PARRA BAEZ</t>
+          <t>E. ORTIZ TORRES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7364</v>
+        <v>2.2464</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5724</v>
+        <v>2.427</v>
       </c>
       <c r="F18" t="n">
-        <v>0.164</v>
+        <v>-0.1805</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9518</v>
+        <v>3.6973</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1709</v>
+        <v>2.9421</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1228</v>
+        <v>0.7552</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6953</v>
+        <v>3.6622</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8428</v>
+        <v>1.7943</v>
       </c>
       <c r="L18" t="n">
-        <v>3.5382</v>
+        <v>1.8679</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7435</v>
+        <v>0.0351</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3281</v>
+        <v>1.1479</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4154</v>
+        <v>-1.1127</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.616</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.2588</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1604</v>
+        <v>-0.0135</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.283</v>
+        <v>-0.3953</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4434</v>
+        <v>0.3818</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>1.4189</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1786</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. ORTIZ TORRES</t>
+          <t>J. PARRA BAEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4967</v>
+        <v>1.9422</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1132</v>
+        <v>1.3632</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6163999999999999</v>
+        <v>0.579</v>
       </c>
       <c r="G19" t="n">
-        <v>3.6973</v>
+        <v>1.9518</v>
       </c>
       <c r="H19" t="n">
-        <v>2.9421</v>
+        <v>-1.1709</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7552</v>
+        <v>3.1228</v>
       </c>
       <c r="J19" t="n">
-        <v>3.6622</v>
+        <v>2.6953</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7943</v>
+        <v>-0.8428</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8679</v>
+        <v>3.5382</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0351</v>
+        <v>-0.7435</v>
       </c>
       <c r="N19" t="n">
-        <v>1.1479</v>
+        <v>-0.3281</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1127</v>
+        <v>-0.4154</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.4374</v>
+        <v>-0.616</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.2588</v>
       </c>
       <c r="R19" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7632</v>
+        <v>0.3662</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7091</v>
+        <v>-0.4922</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0541</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="W19" t="n">
         <v>1.4189</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.4189</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ABDULSALAM</t>
+          <t>M. ALVAREZ PUERTAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0116</v>
+        <v>1.067</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1388</v>
+        <v>0.1848</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1504</v>
+        <v>0.8822</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2752</v>
+        <v>0.5269</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3536</v>
+        <v>-1.6122</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6288</v>
+        <v>2.1392</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9449</v>
+        <v>1.15</v>
       </c>
       <c r="K20" t="n">
-        <v>0.182</v>
+        <v>-1.3363</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7629</v>
+        <v>2.4863</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2201</v>
+        <v>-0.6231</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1716</v>
+        <v>-0.2759</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3917</v>
+        <v>-0.3472</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.0801</v>
+        <v>0.616</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.3122</v>
+        <v>-0.4107</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2321</v>
+        <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>2.2499</v>
+        <v>0.2731</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8096</v>
+        <v>-0.2054</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4403</v>
+        <v>0.4786</v>
       </c>
       <c r="V20" t="n">
-        <v>2.117</v>
+        <v>-0.3491</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4189</v>
+        <v>-0.3491</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. ALVAREZ PUERTAS</t>
+          <t>M. ABDULSALAM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9311</v>
+        <v>0.3125</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.129</v>
+        <v>-1.4526</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0601</v>
+        <v>1.7651</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5269</v>
+        <v>-0.2752</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6122</v>
+        <v>0.3536</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1392</v>
+        <v>-0.6288</v>
       </c>
       <c r="J21" t="n">
-        <v>1.15</v>
+        <v>0.9449</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3363</v>
+        <v>0.182</v>
       </c>
       <c r="L21" t="n">
-        <v>2.4863</v>
+        <v>0.7629</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6231</v>
+        <v>-1.2201</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2759</v>
+        <v>0.1716</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3472</v>
+        <v>-1.3917</v>
       </c>
       <c r="P21" t="n">
-        <v>0.616</v>
+        <v>-3.0801</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.4107</v>
+        <v>-4.3122</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1372</v>
+        <v>1.5507</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5192</v>
+        <v>0.4958</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6564</v>
+        <v>1.055</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3491</v>
+        <v>2.117</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3491</v>
+        <v>1.4189</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.05</v>
+        <v>0.308</v>
       </c>
       <c r="E22" t="n">
         <v>-0.1976</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2476</v>
+        <v>0.5057</v>
       </c>
       <c r="G22" t="n">
         <v>0.8659</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6106</v>
+        <v>-0.3525</v>
       </c>
       <c r="T22" t="n">
         <v>0.0077</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6183</v>
+        <v>-0.3603</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5828</v>
+        <v>-0.3613</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5658</v>
+        <v>-0.6704</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.017</v>
+        <v>0.3091</v>
       </c>
       <c r="G23" t="n">
         <v>1.4138</v>
@@ -2248,13 +2248,13 @@
         <v>2.0534</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0774</v>
+        <v>1.2988</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8096</v>
+        <v>0.705</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2678</v>
+        <v>0.5939</v>
       </c>
       <c r="V23" t="n">
         <v>-1.6366</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. NVE MALEVA</t>
+          <t>J. TEJERA TEJO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8867</v>
+        <v>-2.0425</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5274</v>
+        <v>-0.6485</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6407</v>
+        <v>-1.394</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0459</v>
+        <v>0.8847</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3989</v>
+        <v>1.1318</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4448</v>
+        <v>-0.2471</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9809</v>
+        <v>0.8472</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.0993</v>
+        <v>0.0973</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1184</v>
+        <v>0.7498</v>
       </c>
       <c r="M24" t="n">
-        <v>1.0268</v>
+        <v>0.0375</v>
       </c>
       <c r="N24" t="n">
-        <v>0.7004</v>
+        <v>1.0345</v>
       </c>
       <c r="O24" t="n">
-        <v>0.3264</v>
+        <v>-0.997</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.8481</v>
+        <v>-0.616</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2588</v>
+        <v>-1.2321</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="S24" t="n">
-        <v>2.0941</v>
+        <v>0.6354</v>
       </c>
       <c r="T24" t="n">
-        <v>1.7123</v>
+        <v>-0.2636</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3818</v>
+        <v>0.899</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.1786</v>
+        <v>-2.9466</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.1786</v>
+        <v>-2.9466</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. TEJERA TEJO</t>
+          <t>J. NVE MALEVA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.2586</v>
+        <v>-2.1507</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.9623</v>
+        <v>-2.7826</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2964</v>
+        <v>0.6319</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8847</v>
+        <v>0.0459</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1318</v>
+        <v>-0.3989</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2471</v>
+        <v>0.4448</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8472</v>
+        <v>-0.9809</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0973</v>
+        <v>-1.0993</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7498</v>
+        <v>0.1184</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0375</v>
+        <v>1.0268</v>
       </c>
       <c r="N25" t="n">
-        <v>1.0345</v>
+        <v>0.7004</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.997</v>
+        <v>0.3264</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.616</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.2321</v>
+        <v>-2.2588</v>
       </c>
       <c r="R25" t="n">
-        <v>0.616</v>
+        <v>0.4107</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4193</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5774</v>
+        <v>0.457</v>
       </c>
       <c r="U25" t="n">
-        <v>0.9967</v>
+        <v>0.3731</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.9466</v>
+        <v>-1.1786</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.9466</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="26">
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>12.9449</v>
+        <v>13.6422</v>
       </c>
       <c r="E26" t="n">
         <v>2.2799</v>
       </c>
       <c r="F26" t="n">
-        <v>10.665</v>
+        <v>11.3624</v>
       </c>
       <c r="G26" t="n">
         <v>14.5906</v>
       </c>
       <c r="H26" t="n">
-        <v>5.3031</v>
+        <v>5.303099999999999</v>
       </c>
       <c r="I26" t="n">
         <v>9.287700000000001</v>
@@ -2458,13 +2458,13 @@
         <v>14.1742</v>
       </c>
       <c r="K26" t="n">
-        <v>1.7711</v>
+        <v>1.771100000000001</v>
       </c>
       <c r="L26" t="n">
         <v>12.4031</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4164999999999999</v>
+        <v>0.4165</v>
       </c>
       <c r="N26" t="n">
         <v>3.532</v>
@@ -2482,13 +2482,13 @@
         <v>12.3205</v>
       </c>
       <c r="S26" t="n">
-        <v>6.0444</v>
+        <v>6.741699999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1563999999999998</v>
+        <v>-0.1564999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>6.2008</v>
+        <v>6.898299999999999</v>
       </c>
       <c r="V26" t="n">
         <v>1.5501</v>
